--- a/ИД/Завзаказ/1269/КД/1269-1 Шафа/наличие  1269-1.xlsx
+++ b/ИД/Завзаказ/1269/КД/1269-1 Шафа/наличие  1269-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Общие диски\04_ЗавЗакази\2026\1269_Юр-Пак\КД\1269-1 Шафа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050C33A0-259D-4B1E-8F2D-B2AE50810B42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0405A825-AEA0-4600-9682-117E9A9D87A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
